--- a/Assets/Originals/Excels/Goal/GoalMessage.xlsx
+++ b/Assets/Originals/Excels/Goal/GoalMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Goal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2FDC35-4865-412A-BA32-D28D1FC7FC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316FFA69-CE5A-4109-A048-1BA99D805D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -55,6 +55,34 @@
   </si>
   <si>
     <t>このアイテムではないようだ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Collect the Document</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Collect Mystery Items</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Select the item related to the Document.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>This doesn't seem to be the right item.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeJapanese</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageEnglish</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeEnglish</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -383,84 +411,132 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="45.375" customWidth="1"/>
+    <col min="3" max="3" width="19.875" customWidth="1"/>
+    <col min="4" max="4" width="35" customWidth="1"/>
+    <col min="5" max="5" width="18.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="C4">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
+      <c r="C5">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
+      <c r="C6">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Goal/GoalMessage.xlsx
+++ b/Assets/Originals/Excels/Goal/GoalMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Goal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316FFA69-CE5A-4109-A048-1BA99D805D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1FD43F-EB7F-4485-9CEB-3FC9F75F0116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="13">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -45,19 +45,6 @@
     <t>message</t>
   </si>
   <si>
-    <t>ドキュメントを集めてください</t>
-  </si>
-  <si>
-    <t>ミステリーアイテムを集めてください</t>
-  </si>
-  <si>
-    <t>ドキュメントに関係するアイテムを選択せよ</t>
-  </si>
-  <si>
-    <t>このアイテムではないようだ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Collect the Document</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -83,6 +70,22 @@
   </si>
   <si>
     <t>messageSizeEnglish</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドキュメントを&lt;r="あつ"&gt;集&lt;/r&gt;めよ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ミステリーアイテムを&lt;r="あつ"&gt;集&lt;/r&gt;めよ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドキュメントに&lt;r="かんけい"&gt;関係&lt;/r&gt;するアイテムを&lt;r="せんたく"&gt;選択&lt;/r&gt;せよ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このアイテムではない</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -414,7 +417,7 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="45.375" customWidth="1"/>
+    <col min="2" max="2" width="45.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.875" customWidth="1"/>
     <col min="4" max="4" width="35" customWidth="1"/>
     <col min="5" max="5" width="18.875" customWidth="1"/>
@@ -424,17 +427,17 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -446,14 +449,14 @@
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
         <v>2</v>
-      </c>
-      <c r="C3">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
       </c>
       <c r="E3">
         <v>22</v>
@@ -463,31 +466,31 @@
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
       <c r="E4">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
         <v>4</v>
-      </c>
-      <c r="C5">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
       </c>
       <c r="E5">
         <v>22</v>
@@ -497,14 +500,14 @@
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
         <v>5</v>
-      </c>
-      <c r="C6">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
       </c>
       <c r="E6">
         <v>22</v>
@@ -514,7 +517,6 @@
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="1"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">

--- a/Assets/Originals/Excels/Goal/GoalMessage.xlsx
+++ b/Assets/Originals/Excels/Goal/GoalMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Goal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1FD43F-EB7F-4485-9CEB-3FC9F75F0116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6246A9E-DB39-47D8-8D8B-291EAB48F005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -86,6 +86,26 @@
   </si>
   <si>
     <t>このアイテムではない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>收集文件</t>
+  </si>
+  <si>
+    <t>收集神秘物品</t>
+  </si>
+  <si>
+    <t>选择与文件相关的物品</t>
+  </si>
+  <si>
+    <t>这不是正确的物品</t>
+  </si>
+  <si>
+    <t>messageChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeChinese01</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -93,7 +113,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,6 +127,12 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -129,11 +155,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -414,16 +444,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="45.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.875" customWidth="1"/>
     <col min="4" max="4" width="35" customWidth="1"/>
     <col min="5" max="5" width="18.875" customWidth="1"/>
+    <col min="6" max="6" width="24.375" customWidth="1"/>
+    <col min="7" max="7" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -439,13 +471,19 @@
       <c r="E1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -461,8 +499,14 @@
       <c r="E3">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="34.5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -478,8 +522,14 @@
       <c r="E4">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="37.5">
+      <c r="F4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="51">
       <c r="A5">
         <v>3</v>
       </c>
@@ -495,8 +545,14 @@
       <c r="E5">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="34.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -512,33 +568,39 @@
       <c r="E6">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Goal/GoalMessage.xlsx
+++ b/Assets/Originals/Excels/Goal/GoalMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Goal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6246A9E-DB39-47D8-8D8B-291EAB48F005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6139767-92E8-48E9-B6FA-6D6830051F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -106,6 +106,23 @@
   </si>
   <si>
     <t>messageSizeChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>收集檔案</t>
+  </si>
+  <si>
+    <t>選擇與檔案相關的物品</t>
+  </si>
+  <si>
+    <t>這不是正確的物品</t>
+  </si>
+  <si>
+    <t>messageChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeChinese02</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -113,7 +130,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,6 +150,12 @@
       <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -155,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -164,6 +187,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -444,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="45.375" style="1" customWidth="1"/>
@@ -453,9 +481,11 @@
     <col min="5" max="5" width="18.875" customWidth="1"/>
     <col min="6" max="6" width="24.375" customWidth="1"/>
     <col min="7" max="7" width="22.5" customWidth="1"/>
+    <col min="8" max="8" width="27.5" customWidth="1"/>
+    <col min="9" max="9" width="21.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,13 +507,21 @@
       <c r="G1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>1</v>
       </c>
@@ -505,8 +543,14 @@
       <c r="G3" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="34.5">
+      <c r="H3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="32.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -528,8 +572,14 @@
       <c r="G4" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="51">
+      <c r="H4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="47.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -551,8 +601,14 @@
       <c r="G5" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="34.5">
+      <c r="H5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="32.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -574,33 +630,39 @@
       <c r="G6" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Goal/GoalMessage.xlsx
+++ b/Assets/Originals/Excels/Goal/GoalMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Goal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6139767-92E8-48E9-B6FA-6D6830051F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F33BF0-D6C5-479A-9758-BFF0FBFCB7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -123,6 +123,25 @@
   </si>
   <si>
     <t>messageSizeChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSpanish</t>
+  </si>
+  <si>
+    <t>messageSizeSpanish</t>
+  </si>
+  <si>
+    <t>Recoge los Documentos</t>
+  </si>
+  <si>
+    <t>Recoge los Objetos Misteriosos</t>
+  </si>
+  <si>
+    <t>Este no es el objeto correcto</t>
+  </si>
+  <si>
+    <t>Elige el objeto relacionado con el Documento</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -187,11 +206,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -472,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="45.375" style="1" customWidth="1"/>
@@ -483,9 +502,11 @@
     <col min="7" max="7" width="22.5" customWidth="1"/>
     <col min="8" max="8" width="27.5" customWidth="1"/>
     <col min="9" max="9" width="21.375" customWidth="1"/>
+    <col min="10" max="10" width="39.25" customWidth="1"/>
+    <col min="11" max="11" width="20.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,21 +528,27 @@
       <c r="G1" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="4" t="s">
+      <c r="H1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>1</v>
       </c>
@@ -543,14 +570,20 @@
       <c r="G3" s="3">
         <v>22</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="32.25">
+      <c r="I3" s="5">
+        <v>22</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>2</v>
       </c>
@@ -572,14 +605,20 @@
       <c r="G4" s="3">
         <v>22</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="47.25">
+      <c r="I4" s="5">
+        <v>22</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -601,14 +640,20 @@
       <c r="G5" s="3">
         <v>22</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="32.25">
+      <c r="I5" s="5">
+        <v>22</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>4</v>
       </c>
@@ -630,39 +675,45 @@
       <c r="G6" s="3">
         <v>22</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="I6" s="5">
+        <v>22</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Goal/GoalMessage.xlsx
+++ b/Assets/Originals/Excels/Goal/GoalMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Goal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F33BF0-D6C5-479A-9758-BFF0FBFCB7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5209515-8C71-4188-814B-A9435187E7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -143,6 +143,24 @@
   <si>
     <t>Elige el objeto relacionado con el Documento</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messagePortuguese</t>
+  </si>
+  <si>
+    <t>messageSizePortuguese</t>
+  </si>
+  <si>
+    <t>Colete os Documentos</t>
+  </si>
+  <si>
+    <t>Colete os Itens Misteriosos</t>
+  </si>
+  <si>
+    <t>Selecione o item relacionado ao Documento</t>
+  </si>
+  <si>
+    <t>Este não é o item correto</t>
   </si>
 </sst>
 </file>
@@ -491,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="45.375" style="1" customWidth="1"/>
@@ -504,9 +522,11 @@
     <col min="9" max="9" width="21.375" customWidth="1"/>
     <col min="10" max="10" width="39.25" customWidth="1"/>
     <col min="11" max="11" width="20.75" customWidth="1"/>
+    <col min="12" max="12" width="41.25" customWidth="1"/>
+    <col min="13" max="13" width="23.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -534,21 +554,27 @@
       <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>1</v>
       </c>
@@ -576,14 +602,20 @@
       <c r="I3" s="5">
         <v>22</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="K3">
+        <v>22</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>2</v>
       </c>
@@ -611,14 +643,20 @@
       <c r="I4" s="5">
         <v>22</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="37.5">
+      <c r="K4">
+        <v>22</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -646,14 +684,20 @@
       <c r="I5" s="5">
         <v>22</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="K5">
+        <v>22</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>4</v>
       </c>
@@ -681,39 +725,45 @@
       <c r="I6" s="5">
         <v>22</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" t="s">
         <v>28</v>
       </c>
-      <c r="K6" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="K6">
+        <v>22</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:13">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:13">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:13">
       <c r="A12">
         <v>10</v>
       </c>
